--- a/public/templates/ha_primer_import_template.xlsx
+++ b/public/templates/ha_primer_import_template.xlsx
@@ -1,41 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidrr/workspace/bbi-lab/bbi-lims-sge/public/templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6A6E78-5B74-394B-8E5E-6BA91941DC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="HA Primers" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Primer Name</t>
+  </si>
+  <si>
+    <t>Sequence</t>
+  </si>
+  <si>
+    <t>Forward/Reverse</t>
+  </si>
+  <si>
+    <t>Cloning Strategy</t>
+  </si>
+  <si>
+    <t>Target Name(s)</t>
+  </si>
+  <si>
+    <t>Ordered On</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>HA_Gene1_F</t>
+  </si>
+  <si>
+    <t>ATCGATCGATCGATCGATCG</t>
+  </si>
+  <si>
+    <t>forward</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>Gene1_Target1, Gene1_Target2</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>Sample row - do not import</t>
+  </si>
+  <si>
+    <t>HA_Storage_Plate_1</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Well/Tube Coordinates</t>
+  </si>
+  <si>
+    <t>Plate/Storage Box Name</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,13 +91,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +134,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,281 +484,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I201"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="35.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.83203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Primer Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Sequence</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Forward/Reverse</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Cloning Strategy</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Target Name(s)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Ordered On</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Plate Storage Box Name</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Well Tube Coordinates</v>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>HA_Gene1_F</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ATCGATCGATCGATCGATCG</v>
-      </c>
-      <c r="C2" t="str">
-        <v>forward</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Gibson</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Gene1_Target1, Gene1_Target2</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-01-01</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Sample row - do not import</v>
-      </c>
-      <c r="H2" t="str">
-        <v>HA_Storage_Plate_1</v>
-      </c>
-      <c r="I2" t="str">
-        <v>A1</v>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
   </sheetData>
-  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1" formatColumns="0" formatRows="0" formatCells="0" insertColumns="0" insertRows="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" deleteColumns="0" deleteRows="0" sort="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I201"/>
+    <ignoredError sqref="A2:I201 A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>